--- a/results/intensive_linear_95p_weighted_strong/estimates/log_intensive_linear_95p_weighted_strong_b1_1000perm_estimates.xlsx
+++ b/results/intensive_linear_95p_weighted_strong/estimates/log_intensive_linear_95p_weighted_strong_b1_1000perm_estimates.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F52"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -389,14 +389,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ver</t>
+          <t>total_reactions</t>
         </is>
       </c>
       <c r="B2">
-        <v>0.03269100301442745</v>
+        <v>-0.0320627916946496</v>
       </c>
       <c r="C2">
-        <v>0.05007485128449538</v>
+        <v>0.1774203738780718</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -405,7 +405,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>log Verifiable Posts + Shares</t>
+          <t>log(Total reactions)</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -417,14 +417,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>non_ver</t>
+          <t>total_comments</t>
         </is>
       </c>
       <c r="B3">
-        <v>0.05281000990507505</v>
+        <v>0.05260976996718535</v>
       </c>
       <c r="C3">
-        <v>0.07846932765862187</v>
+        <v>0.06250884490039575</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -433,7 +433,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>log Non Verifiable Posts + Shares</t>
+          <t>log(Total comments)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -445,14 +445,14 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>total_shares</t>
         </is>
       </c>
       <c r="B4">
-        <v>0.03547269871818406</v>
+        <v>-0.08186521115182933</v>
       </c>
       <c r="C4">
-        <v>0.03363146083312536</v>
+        <v>0.1792026000378192</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -461,7 +461,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>log True Posts + Shares</t>
+          <t>log(Total shares)</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -473,14 +473,14 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>fake</t>
+          <t>n_posts</t>
         </is>
       </c>
       <c r="B5">
-        <v>0.02076617454432404</v>
+        <v>0.04073088464542036</v>
       </c>
       <c r="C5">
-        <v>0.0464766052412816</v>
+        <v>0.08653273479085627</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -489,7 +489,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>log Fake Posts + Shares</t>
+          <t>log(Number of posts + shares)</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -501,14 +501,14 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>n_posts</t>
+          <t>eng</t>
         </is>
       </c>
       <c r="B6">
-        <v>0.03987009213616211</v>
+        <v>0.05095844055907067</v>
       </c>
       <c r="C6">
-        <v>0.08663118669970893</v>
+        <v>0.08119115071782328</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -517,7 +517,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>log Number of Posts + Shares</t>
+          <t>log(Number of posts + shares, English)</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -529,28 +529,28 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ver</t>
+          <t>verifiability</t>
         </is>
       </c>
       <c r="B7">
-        <v>-0.005491564846234392</v>
+        <v>0.02853065848337561</v>
       </c>
       <c r="C7">
-        <v>0.04247051834110405</v>
+        <v>0.05070744860187826</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>stage3_4</t>
+          <t>stage1_2</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>log Verifiable Posts + Shares</t>
+          <t>log(Verifiable posts + shares)</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Weeks 5-8</t>
+          <t>Weeks 1-4</t>
         </is>
       </c>
     </row>
@@ -561,24 +561,24 @@
         </is>
       </c>
       <c r="B8">
-        <v>0.004617710038966171</v>
+        <v>0.05307685952439349</v>
       </c>
       <c r="C8">
-        <v>0.057255340025313</v>
+        <v>0.0789813980236526</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>stage3_4</t>
+          <t>stage1_2</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>log Non Verifiable Posts + Shares</t>
+          <t>log(Non-verifiable posts + shares)</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Weeks 5-8</t>
+          <t>Weeks 1-4</t>
         </is>
       </c>
     </row>
@@ -589,24 +589,24 @@
         </is>
       </c>
       <c r="B9">
-        <v>0.0194253551057827</v>
+        <v>0.03431883748682826</v>
       </c>
       <c r="C9">
-        <v>0.03327522476368903</v>
+        <v>0.03464762667144753</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>stage3_4</t>
+          <t>stage1_2</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>log True Posts + Shares</t>
+          <t>log(True posts + shares)</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Weeks 5-8</t>
+          <t>Weeks 1-4</t>
         </is>
       </c>
     </row>
@@ -617,190 +617,1198 @@
         </is>
       </c>
       <c r="B10">
-        <v>-0.01331375599485924</v>
+        <v>0.01790794246003864</v>
       </c>
       <c r="C10">
-        <v>0.041511058832657</v>
+        <v>0.04687440636417355</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>stage3_4</t>
+          <t>stage1_2</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>log Fake Posts + Shares</t>
+          <t>log(Fake posts + shares)</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Weeks 5-8</t>
+          <t>Weeks 1-4</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>n_posts</t>
+          <t>n_posts_covid</t>
         </is>
       </c>
       <c r="B11">
-        <v>0.004273396457822267</v>
+        <v>-0.003147513038369688</v>
       </c>
       <c r="C11">
-        <v>0.05832586160408919</v>
+        <v>0.01073522437795862</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>stage3_4</t>
+          <t>stage1_2</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>log Number of Posts + Shares</t>
+          <t>log(COVID posts + shares)</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Weeks 5-8</t>
+          <t>Weeks 1-4</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ver</t>
+          <t>pos_b_covid</t>
         </is>
       </c>
       <c r="B12">
-        <v>0.007859212408865005</v>
+        <v>0.00207130368660845</v>
       </c>
       <c r="C12">
-        <v>0.04700450934065852</v>
+        <v>0.007266425403134667</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>stage5_6</t>
+          <t>stage1_2</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>log Verifiable Posts + Shares</t>
+          <t>log(Positive COVID posts + shares)</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Weeks 9-12</t>
+          <t>Weeks 1-4</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>non_ver</t>
+          <t>neutral_b_covid</t>
         </is>
       </c>
       <c r="B13">
-        <v>-0.04607646601114063</v>
+        <v>-0.003700440048172055</v>
       </c>
       <c r="C13">
-        <v>0.05883757386057418</v>
+        <v>0.005428115986595215</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>stage5_6</t>
+          <t>stage1_2</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>log Non Verifiable Posts + Shares</t>
+          <t>log(Neutral COVID posts + shares)</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Weeks 9-12</t>
+          <t>Weeks 1-4</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>neg_b_covid</t>
         </is>
       </c>
       <c r="B14">
-        <v>0.04477946426409828</v>
+        <v>-0.002906163468720074</v>
       </c>
       <c r="C14">
-        <v>0.03556052413447282</v>
+        <v>0.007082359446690788</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>stage5_6</t>
+          <t>stage1_2</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>log True Posts + Shares</t>
+          <t>log(Negative COVID posts + shares)</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Weeks 9-12</t>
+          <t>Weeks 1-4</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>fake</t>
+          <t>n_posts_vax</t>
         </is>
       </c>
       <c r="B15">
-        <v>-0.01245079305428784</v>
+        <v>0.0005670019087741012</v>
       </c>
       <c r="C15">
-        <v>0.04269550352852559</v>
+        <v>0.005875849035801242</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>stage5_6</t>
+          <t>stage1_2</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>log Fake Posts + Shares</t>
+          <t>log(Vaccine posts + shares)</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Weeks 9-12</t>
+          <t>Weeks 1-4</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>pos_b_vax</t>
+        </is>
+      </c>
+      <c r="B16">
+        <v>0.0003056327660040838</v>
+      </c>
+      <c r="C16">
+        <v>0.004053132053539257</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>stage1_2</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>log(Positive vaccine posts + shares)</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Weeks 1-4</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>neutral_b_vax</t>
+        </is>
+      </c>
+      <c r="B17">
+        <v>3.147124627960769e-05</v>
+      </c>
+      <c r="C17">
+        <v>0.003100070028324927</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>stage1_2</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>log(Neutral vaccine posts + shares)</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Weeks 1-4</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>neg_b_vax</t>
+        </is>
+      </c>
+      <c r="B18">
+        <v>-0.000315335402378977</v>
+      </c>
+      <c r="C18">
+        <v>0.002712755619499187</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>stage1_2</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>log(Negative vaccine posts + shares)</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Weeks 1-4</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>total_reactions</t>
+        </is>
+      </c>
+      <c r="B19">
+        <v>-0.189265632258156</v>
+      </c>
+      <c r="C19">
+        <v>0.1454917865538141</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>stage3_4</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>log(Total reactions)</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Weeks 5-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>total_comments</t>
+        </is>
+      </c>
+      <c r="B20">
+        <v>0.04686479808333388</v>
+      </c>
+      <c r="C20">
+        <v>0.06495057809914041</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>stage3_4</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>log(Total comments)</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Weeks 5-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>total_shares</t>
+        </is>
+      </c>
+      <c r="B21">
+        <v>-0.2236430950715811</v>
+      </c>
+      <c r="C21">
+        <v>0.1589514270305883</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>stage3_4</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>log(Total shares)</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Weeks 5-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>n_posts</t>
         </is>
       </c>
-      <c r="B16">
-        <v>-0.04843467109344461</v>
-      </c>
-      <c r="C16">
-        <v>0.06206873048376703</v>
-      </c>
-      <c r="D16" t="inlineStr">
+      <c r="B22">
+        <v>0.005303658647003344</v>
+      </c>
+      <c r="C22">
+        <v>0.05835854323174107</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>stage3_4</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>log(Number of posts + shares)</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Weeks 5-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>eng</t>
+        </is>
+      </c>
+      <c r="B23">
+        <v>-0.004354749442706089</v>
+      </c>
+      <c r="C23">
+        <v>0.05788526543674414</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>stage3_4</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>log(Number of posts + shares, English)</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Weeks 5-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>verifiability</t>
+        </is>
+      </c>
+      <c r="B24">
+        <v>-0.01051593453843292</v>
+      </c>
+      <c r="C24">
+        <v>0.04223372986044118</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>stage3_4</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>log(Verifiable posts + shares)</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Weeks 5-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>non_ver</t>
+        </is>
+      </c>
+      <c r="B25">
+        <v>0.004910038913203502</v>
+      </c>
+      <c r="C25">
+        <v>0.05719543045050521</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>stage3_4</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>log(Non-verifiable posts + shares)</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Weeks 5-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="B26">
+        <v>0.01773219939478852</v>
+      </c>
+      <c r="C26">
+        <v>0.03323026488860486</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>stage3_4</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>log(True posts + shares)</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Weeks 5-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>fake</t>
+        </is>
+      </c>
+      <c r="B27">
+        <v>-0.01664176308490841</v>
+      </c>
+      <c r="C27">
+        <v>0.04180217504722795</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>stage3_4</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>log(Fake posts + shares)</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Weeks 5-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>n_posts_covid</t>
+        </is>
+      </c>
+      <c r="B28">
+        <v>-0.008609734213792547</v>
+      </c>
+      <c r="C28">
+        <v>0.0163617121837149</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>stage3_4</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>log(COVID posts + shares)</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Weeks 5-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>pos_b_covid</t>
+        </is>
+      </c>
+      <c r="B29">
+        <v>-0.00583925432491057</v>
+      </c>
+      <c r="C29">
+        <v>0.0103990475524568</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>stage3_4</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>log(Positive COVID posts + shares)</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Weeks 5-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>neutral_b_covid</t>
+        </is>
+      </c>
+      <c r="B30">
+        <v>-0.007744856229982228</v>
+      </c>
+      <c r="C30">
+        <v>0.008508243244087384</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>stage3_4</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>log(Neutral COVID posts + shares)</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Weeks 5-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>neg_b_covid</t>
+        </is>
+      </c>
+      <c r="B31">
+        <v>-6.792865599920123e-05</v>
+      </c>
+      <c r="C31">
+        <v>0.008498030976460728</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>stage3_4</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>log(Negative COVID posts + shares)</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Weeks 5-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>n_posts_vax</t>
+        </is>
+      </c>
+      <c r="B32">
+        <v>-0.001121142964001032</v>
+      </c>
+      <c r="C32">
+        <v>0.002897002033764811</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>stage3_4</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>log(Vaccine posts + shares)</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Weeks 5-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>pos_b_vax</t>
+        </is>
+      </c>
+      <c r="B33">
+        <v>-0.0001752003623818677</v>
+      </c>
+      <c r="C33">
+        <v>0.00184754790060946</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>stage3_4</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>log(Positive vaccine posts + shares)</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Weeks 5-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>neutral_b_vax</t>
+        </is>
+      </c>
+      <c r="B34">
+        <v>-0.001665163532363147</v>
+      </c>
+      <c r="C34">
+        <v>0.001376855982418892</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>stage3_4</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>log(Neutral vaccine posts + shares)</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Weeks 5-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>neg_b_vax</t>
+        </is>
+      </c>
+      <c r="B35">
+        <v>0.0003369390486624596</v>
+      </c>
+      <c r="C35">
+        <v>0.001664430299968864</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>stage3_4</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>log(Negative vaccine posts + shares)</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Weeks 5-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>total_reactions</t>
+        </is>
+      </c>
+      <c r="B36">
+        <v>-0.06326807018730571</v>
+      </c>
+      <c r="C36">
+        <v>0.1535478445218412</v>
+      </c>
+      <c r="D36" t="inlineStr">
         <is>
           <t>stage5_6</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>log Number of Posts + Shares</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>log(Total reactions)</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Weeks 9-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>total_comments</t>
+        </is>
+      </c>
+      <c r="B37">
+        <v>0.02815845751481381</v>
+      </c>
+      <c r="C37">
+        <v>0.06703077402328818</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>stage5_6</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>log(Total comments)</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Weeks 9-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>total_shares</t>
+        </is>
+      </c>
+      <c r="B38">
+        <v>-0.0809369029927461</v>
+      </c>
+      <c r="C38">
+        <v>0.1609947623977074</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>stage5_6</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>log(Total shares)</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Weeks 9-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>n_posts</t>
+        </is>
+      </c>
+      <c r="B39">
+        <v>-0.04742308461616732</v>
+      </c>
+      <c r="C39">
+        <v>0.0619913492622069</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>stage5_6</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>log(Number of posts + shares)</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Weeks 9-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>eng</t>
+        </is>
+      </c>
+      <c r="B40">
+        <v>-0.04629667405975282</v>
+      </c>
+      <c r="C40">
+        <v>0.06182592369182809</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>stage5_6</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>log(Number of posts + shares, English)</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Weeks 9-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>verifiability</t>
+        </is>
+      </c>
+      <c r="B41">
+        <v>0.003127177743141304</v>
+      </c>
+      <c r="C41">
+        <v>0.04628938230406156</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>stage5_6</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>log(Verifiable posts + shares)</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Weeks 9-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>non_ver</t>
+        </is>
+      </c>
+      <c r="B42">
+        <v>-0.04581437451149305</v>
+      </c>
+      <c r="C42">
+        <v>0.05847065434944601</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>stage5_6</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>log(Non-verifiable posts + shares)</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Weeks 9-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="B43">
+        <v>0.04323284173521973</v>
+      </c>
+      <c r="C43">
+        <v>0.03510022824238234</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>stage5_6</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>log(True posts + shares)</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Weeks 9-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>fake</t>
+        </is>
+      </c>
+      <c r="B44">
+        <v>-0.01550624596621029</v>
+      </c>
+      <c r="C44">
+        <v>0.04256413999464524</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>stage5_6</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>log(Fake posts + shares)</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Weeks 9-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>n_posts_covid</t>
+        </is>
+      </c>
+      <c r="B45">
+        <v>0.00143661076472409</v>
+      </c>
+      <c r="C45">
+        <v>0.0140347625779279</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>stage5_6</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>log(COVID posts + shares)</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Weeks 9-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>pos_b_covid</t>
+        </is>
+      </c>
+      <c r="B46">
+        <v>-0.001455707203483658</v>
+      </c>
+      <c r="C46">
+        <v>0.007516168066713361</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>stage5_6</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>log(Positive COVID posts + shares)</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Weeks 9-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>neutral_b_covid</t>
+        </is>
+      </c>
+      <c r="B47">
+        <v>0.004458290349948373</v>
+      </c>
+      <c r="C47">
+        <v>0.009079200672481105</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>stage5_6</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>log(Neutral COVID posts + shares)</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Weeks 9-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>neg_b_covid</t>
+        </is>
+      </c>
+      <c r="B48">
+        <v>-0.003416857057498427</v>
+      </c>
+      <c r="C48">
+        <v>0.008624895655854619</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>stage5_6</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>log(Negative COVID posts + shares)</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Weeks 9-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>n_posts_vax</t>
+        </is>
+      </c>
+      <c r="B49">
+        <v>0.002142016006786111</v>
+      </c>
+      <c r="C49">
+        <v>0.003970833483670193</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>stage5_6</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>log(Vaccine posts + shares)</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Weeks 9-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>pos_b_vax</t>
+        </is>
+      </c>
+      <c r="B50">
+        <v>-0.0003556873663025886</v>
+      </c>
+      <c r="C50">
+        <v>0.001763189841147962</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>stage5_6</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>log(Positive vaccine posts + shares)</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Weeks 9-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>neutral_b_vax</t>
+        </is>
+      </c>
+      <c r="B51">
+        <v>0.001636420393017839</v>
+      </c>
+      <c r="C51">
+        <v>0.002082758946888174</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>stage5_6</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>log(Neutral vaccine posts + shares)</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Weeks 9-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>neg_b_vax</t>
+        </is>
+      </c>
+      <c r="B52">
+        <v>0.0004481587510305401</v>
+      </c>
+      <c r="C52">
+        <v>0.002477950296069913</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>stage5_6</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>log(Negative vaccine posts + shares)</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
         <is>
           <t>Weeks 9-12</t>
         </is>
